--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre11.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="88">
   <si>
     <t>Scenario</t>
   </si>
@@ -265,7 +265,16 @@
     <t>agah</t>
   </si>
   <si>
-    <t>MALERKOTLA</t>
+    <t>Amritsar</t>
+  </si>
+  <si>
+    <t>Fazilka</t>
+  </si>
+  <si>
+    <t>Jalandhar</t>
+  </si>
+  <si>
+    <t>Malerkotla</t>
   </si>
   <si>
     <t>Paddy</t>
@@ -729,7 +738,7 @@
         <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -741,7 +750,7 @@
         <v>74.91584450000001</v>
       </c>
       <c r="R2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S2">
         <v>50000</v>
@@ -788,7 +797,7 @@
         <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -800,7 +809,7 @@
         <v>74.588493</v>
       </c>
       <c r="R3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S3">
         <v>50000</v>
@@ -847,7 +856,7 @@
         <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -859,7 +868,7 @@
         <v>74.18214294000001</v>
       </c>
       <c r="R4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S4">
         <v>90000</v>
@@ -906,7 +915,7 @@
         <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>
@@ -918,7 +927,7 @@
         <v>74.18094151</v>
       </c>
       <c r="R5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S5">
         <v>60000</v>
@@ -965,7 +974,7 @@
         <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O6" t="s">
         <v>27</v>
@@ -977,7 +986,7 @@
         <v>74.18085842000001</v>
       </c>
       <c r="R6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S6">
         <v>120000</v>
@@ -1024,7 +1033,7 @@
         <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O7" t="s">
         <v>27</v>
@@ -1036,7 +1045,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S7">
         <v>33610</v>
@@ -1083,7 +1092,7 @@
         <v>21</v>
       </c>
       <c r="N8" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O8" t="s">
         <v>27</v>
@@ -1095,7 +1104,7 @@
         <v>74.18315728</v>
       </c>
       <c r="R8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S8">
         <v>150000</v>
@@ -1142,7 +1151,7 @@
         <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O9" t="s">
         <v>27</v>
@@ -1154,7 +1163,7 @@
         <v>74.161942</v>
       </c>
       <c r="R9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S9">
         <v>143264</v>
@@ -1201,7 +1210,7 @@
         <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O10" t="s">
         <v>27</v>
@@ -1213,7 +1222,7 @@
         <v>74.20908439</v>
       </c>
       <c r="R10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S10">
         <v>48247.5</v>
@@ -1260,7 +1269,7 @@
         <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O11" t="s">
         <v>27</v>
@@ -1272,7 +1281,7 @@
         <v>74.206666</v>
       </c>
       <c r="R11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S11">
         <v>23588</v>
@@ -1319,7 +1328,7 @@
         <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O12" t="s">
         <v>27</v>
@@ -1331,7 +1340,7 @@
         <v>74.18014506</v>
       </c>
       <c r="R12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S12">
         <v>73860.5</v>
@@ -1378,7 +1387,7 @@
         <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O13" t="s">
         <v>27</v>
@@ -1390,7 +1399,7 @@
         <v>74.161942</v>
       </c>
       <c r="R13" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S13">
         <v>37309</v>
@@ -1437,7 +1446,7 @@
         <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O14" t="s">
         <v>27</v>
@@ -1449,7 +1458,7 @@
         <v>74.161942</v>
       </c>
       <c r="R14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S14">
         <v>18025.5</v>
@@ -1496,7 +1505,7 @@
         <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O15" t="s">
         <v>27</v>
@@ -1508,7 +1517,7 @@
         <v>74.20908439</v>
       </c>
       <c r="R15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15">
         <v>16177.5</v>
@@ -1555,7 +1564,7 @@
         <v>21</v>
       </c>
       <c r="N16" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O16" t="s">
         <v>27</v>
@@ -1567,7 +1576,7 @@
         <v>74.20888524</v>
       </c>
       <c r="R16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S16">
         <v>33588.5</v>
@@ -1614,7 +1623,7 @@
         <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O17" t="s">
         <v>27</v>
@@ -1626,7 +1635,7 @@
         <v>74.183232</v>
       </c>
       <c r="R17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S17">
         <v>13129</v>
@@ -1673,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O18" t="s">
         <v>27</v>
@@ -1685,7 +1694,7 @@
         <v>74.161942</v>
       </c>
       <c r="R18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S18">
         <v>28578.5</v>
@@ -1732,7 +1741,7 @@
         <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O19" t="s">
         <v>27</v>
@@ -1744,7 +1753,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S19">
         <v>18038</v>
@@ -1791,7 +1800,7 @@
         <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O20" t="s">
         <v>27</v>
@@ -1803,7 +1812,7 @@
         <v>74.161942</v>
       </c>
       <c r="R20" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S20">
         <v>44568.5</v>
@@ -1850,7 +1859,7 @@
         <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O21" t="s">
         <v>27</v>
@@ -1862,7 +1871,7 @@
         <v>74.206666</v>
       </c>
       <c r="R21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S21">
         <v>25216</v>
@@ -1909,7 +1918,7 @@
         <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O22" t="s">
         <v>27</v>
@@ -1921,7 +1930,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S22">
         <v>44802</v>
@@ -1968,7 +1977,7 @@
         <v>21</v>
       </c>
       <c r="N23" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O23" t="s">
         <v>27</v>
@@ -1980,7 +1989,7 @@
         <v>74.161942</v>
       </c>
       <c r="R23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S23">
         <v>30276.5</v>
@@ -2027,7 +2036,7 @@
         <v>21</v>
       </c>
       <c r="N24" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O24" t="s">
         <v>27</v>
@@ -2039,7 +2048,7 @@
         <v>74.20888524</v>
       </c>
       <c r="R24" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S24">
         <v>19961.5</v>
@@ -2086,7 +2095,7 @@
         <v>21</v>
       </c>
       <c r="N25" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O25" t="s">
         <v>27</v>
@@ -2098,7 +2107,7 @@
         <v>74.20908439</v>
       </c>
       <c r="R25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S25">
         <v>64381</v>
@@ -2145,7 +2154,7 @@
         <v>21</v>
       </c>
       <c r="N26" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O26" t="s">
         <v>27</v>
@@ -2157,7 +2166,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S26">
         <v>39817.5</v>
@@ -2204,7 +2213,7 @@
         <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O27" t="s">
         <v>27</v>
@@ -2216,7 +2225,7 @@
         <v>74.183232</v>
       </c>
       <c r="R27" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S27">
         <v>10375.5</v>
@@ -2263,7 +2272,7 @@
         <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O28" t="s">
         <v>27</v>
@@ -2275,7 +2284,7 @@
         <v>74.161942</v>
       </c>
       <c r="R28" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S28">
         <v>100949.5</v>
@@ -2322,7 +2331,7 @@
         <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O29" t="s">
         <v>27</v>
@@ -2334,7 +2343,7 @@
         <v>74.17723581</v>
       </c>
       <c r="R29" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S29">
         <v>36622.5</v>
@@ -2381,7 +2390,7 @@
         <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O30" t="s">
         <v>27</v>
@@ -2393,7 +2402,7 @@
         <v>74.18014506</v>
       </c>
       <c r="R30" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S30">
         <v>11652.5</v>
@@ -2440,7 +2449,7 @@
         <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O31" t="s">
         <v>27</v>
@@ -2452,7 +2461,7 @@
         <v>74.161942</v>
       </c>
       <c r="R31" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S31">
         <v>16592.5</v>
@@ -2499,7 +2508,7 @@
         <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O32" t="s">
         <v>27</v>
@@ -2511,7 +2520,7 @@
         <v>74.161942</v>
       </c>
       <c r="R32" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S32">
         <v>21311</v>
@@ -2558,7 +2567,7 @@
         <v>21</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O33" t="s">
         <v>27</v>
@@ -2570,7 +2579,7 @@
         <v>74.20908439</v>
       </c>
       <c r="R33" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S33">
         <v>34094</v>
@@ -2617,7 +2626,7 @@
         <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O34" t="s">
         <v>27</v>
@@ -2629,7 +2638,7 @@
         <v>74.183232</v>
       </c>
       <c r="R34" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S34">
         <v>10795.5</v>
@@ -2676,7 +2685,7 @@
         <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O35" t="s">
         <v>27</v>
@@ -2688,7 +2697,7 @@
         <v>74.18230296</v>
       </c>
       <c r="R35" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S35">
         <v>21605.5</v>
@@ -2735,7 +2744,7 @@
         <v>21</v>
       </c>
       <c r="N36" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O36" t="s">
         <v>27</v>
@@ -2747,7 +2756,7 @@
         <v>74.206666</v>
       </c>
       <c r="R36" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S36">
         <v>71196</v>
@@ -2794,7 +2803,7 @@
         <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O37" t="s">
         <v>27</v>
@@ -2806,7 +2815,7 @@
         <v>74.161942</v>
       </c>
       <c r="R37" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S37">
         <v>2489</v>
@@ -2853,7 +2862,7 @@
         <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O38" t="s">
         <v>27</v>
@@ -2865,7 +2874,7 @@
         <v>74.161942</v>
       </c>
       <c r="R38" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S38">
         <v>34208</v>
@@ -2912,7 +2921,7 @@
         <v>21</v>
       </c>
       <c r="N39" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O39" t="s">
         <v>27</v>
@@ -2924,7 +2933,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R39" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S39">
         <v>54819.5</v>
@@ -2971,7 +2980,7 @@
         <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O40" t="s">
         <v>27</v>
@@ -2983,7 +2992,7 @@
         <v>74.161942</v>
       </c>
       <c r="R40" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S40">
         <v>37768</v>
@@ -3030,7 +3039,7 @@
         <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O41" t="s">
         <v>27</v>
@@ -3042,7 +3051,7 @@
         <v>74.161942</v>
       </c>
       <c r="R41" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S41">
         <v>29874.5</v>
@@ -3089,7 +3098,7 @@
         <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O42" t="s">
         <v>27</v>
@@ -3101,7 +3110,7 @@
         <v>74.161942</v>
       </c>
       <c r="R42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S42">
         <v>56983.5</v>
@@ -3148,7 +3157,7 @@
         <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O43" t="s">
         <v>27</v>
@@ -3160,7 +3169,7 @@
         <v>74.161942</v>
       </c>
       <c r="R43" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S43">
         <v>23195.5</v>
@@ -3207,7 +3216,7 @@
         <v>21</v>
       </c>
       <c r="N44" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O44" t="s">
         <v>27</v>
@@ -3219,7 +3228,7 @@
         <v>74.161942</v>
       </c>
       <c r="R44" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S44">
         <v>57368</v>
@@ -3266,7 +3275,7 @@
         <v>21</v>
       </c>
       <c r="N45" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O45" t="s">
         <v>27</v>
@@ -3278,7 +3287,7 @@
         <v>74.18014506</v>
       </c>
       <c r="R45" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S45">
         <v>2487</v>
@@ -3325,7 +3334,7 @@
         <v>21</v>
       </c>
       <c r="N46" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O46" t="s">
         <v>27</v>
@@ -3337,7 +3346,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R46" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S46">
         <v>29195</v>
@@ -3384,7 +3393,7 @@
         <v>21</v>
       </c>
       <c r="N47" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O47" t="s">
         <v>27</v>
@@ -3396,7 +3405,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R47" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S47">
         <v>26795</v>
@@ -3443,7 +3452,7 @@
         <v>21</v>
       </c>
       <c r="N48" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O48" t="s">
         <v>27</v>
@@ -3455,7 +3464,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R48" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S48">
         <v>7950</v>
@@ -3502,7 +3511,7 @@
         <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O49" t="s">
         <v>27</v>
@@ -3514,7 +3523,7 @@
         <v>74.18014506</v>
       </c>
       <c r="R49" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S49">
         <v>5500</v>
@@ -3561,7 +3570,7 @@
         <v>21</v>
       </c>
       <c r="N50" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O50" t="s">
         <v>27</v>
@@ -3573,7 +3582,7 @@
         <v>74.161942</v>
       </c>
       <c r="R50" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S50">
         <v>12630.5</v>
@@ -3620,7 +3629,7 @@
         <v>21</v>
       </c>
       <c r="N51" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O51" t="s">
         <v>27</v>
@@ -3632,7 +3641,7 @@
         <v>74.161942</v>
       </c>
       <c r="R51" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S51">
         <v>13803</v>
@@ -3679,7 +3688,7 @@
         <v>21</v>
       </c>
       <c r="N52" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O52" t="s">
         <v>27</v>
@@ -3691,7 +3700,7 @@
         <v>74.161942</v>
       </c>
       <c r="R52" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S52">
         <v>9145</v>
@@ -3738,7 +3747,7 @@
         <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O53" t="s">
         <v>27</v>
@@ -3750,7 +3759,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R53" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S53">
         <v>17622.5</v>
@@ -3797,7 +3806,7 @@
         <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O54" t="s">
         <v>27</v>
@@ -3809,7 +3818,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R54" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S54">
         <v>2347.5</v>
@@ -3856,7 +3865,7 @@
         <v>21</v>
       </c>
       <c r="N55" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O55" t="s">
         <v>27</v>
@@ -3868,7 +3877,7 @@
         <v>74.17723581</v>
       </c>
       <c r="R55" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S55">
         <v>40337.5</v>
@@ -3915,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O56" t="s">
         <v>27</v>
@@ -3927,7 +3936,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R56" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S56">
         <v>56502.5</v>
@@ -3974,7 +3983,7 @@
         <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O57" t="s">
         <v>27</v>
@@ -3986,7 +3995,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R57" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S57">
         <v>43110</v>
@@ -4033,7 +4042,7 @@
         <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O58" t="s">
         <v>27</v>
@@ -4045,7 +4054,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R58" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S58">
         <v>128218</v>
@@ -4092,7 +4101,7 @@
         <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O59" t="s">
         <v>27</v>
@@ -4104,7 +4113,7 @@
         <v>74.16401603</v>
       </c>
       <c r="R59" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S59">
         <v>62709.5</v>
@@ -4151,7 +4160,7 @@
         <v>21</v>
       </c>
       <c r="N60" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O60" t="s">
         <v>27</v>
@@ -4163,7 +4172,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R60" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S60">
         <v>47189.5</v>
@@ -4210,7 +4219,7 @@
         <v>21</v>
       </c>
       <c r="N61" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="O61" t="s">
         <v>27</v>
@@ -4222,7 +4231,7 @@
         <v>75.685958</v>
       </c>
       <c r="R61" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S61">
         <v>21500</v>
@@ -4269,7 +4278,7 @@
         <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O62" t="s">
         <v>27</v>
@@ -4281,7 +4290,7 @@
         <v>74.453514</v>
       </c>
       <c r="R62" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S62">
         <v>88594</v>
@@ -4328,7 +4337,7 @@
         <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O63" t="s">
         <v>27</v>
@@ -4340,7 +4349,7 @@
         <v>74.453514</v>
       </c>
       <c r="R63" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S63">
         <v>10000</v>
@@ -4387,7 +4396,7 @@
         <v>21</v>
       </c>
       <c r="N64" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O64" t="s">
         <v>27</v>
@@ -4399,7 +4408,7 @@
         <v>74.453514</v>
       </c>
       <c r="R64" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S64">
         <v>5000</v>
@@ -4446,7 +4455,7 @@
         <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O65" t="s">
         <v>27</v>
@@ -4458,7 +4467,7 @@
         <v>74.453514</v>
       </c>
       <c r="R65" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S65">
         <v>5000</v>
@@ -4505,7 +4514,7 @@
         <v>21</v>
       </c>
       <c r="N66" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O66" t="s">
         <v>27</v>
@@ -4517,7 +4526,7 @@
         <v>74.453514</v>
       </c>
       <c r="R66" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S66">
         <v>38086</v>
@@ -4564,7 +4573,7 @@
         <v>21</v>
       </c>
       <c r="N67" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O67" t="s">
         <v>27</v>
@@ -4576,7 +4585,7 @@
         <v>74.453514</v>
       </c>
       <c r="R67" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S67">
         <v>30720</v>
@@ -4623,7 +4632,7 @@
         <v>21</v>
       </c>
       <c r="N68" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O68" t="s">
         <v>27</v>
@@ -4635,7 +4644,7 @@
         <v>74.453514</v>
       </c>
       <c r="R68" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S68">
         <v>5127</v>
@@ -4682,7 +4691,7 @@
         <v>21</v>
       </c>
       <c r="N69" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O69" t="s">
         <v>27</v>
@@ -4694,7 +4703,7 @@
         <v>74.453514</v>
       </c>
       <c r="R69" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S69">
         <v>294680</v>
@@ -4741,7 +4750,7 @@
         <v>21</v>
       </c>
       <c r="N70" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O70" t="s">
         <v>27</v>
@@ -4753,7 +4762,7 @@
         <v>74.453514</v>
       </c>
       <c r="R70" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S70">
         <v>16680</v>
@@ -4800,7 +4809,7 @@
         <v>21</v>
       </c>
       <c r="N71" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O71" t="s">
         <v>27</v>
@@ -4812,7 +4821,7 @@
         <v>74.453514</v>
       </c>
       <c r="R71" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S71">
         <v>10000</v>
@@ -4859,7 +4868,7 @@
         <v>21</v>
       </c>
       <c r="N72" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O72" t="s">
         <v>27</v>
@@ -4871,7 +4880,7 @@
         <v>74.453514</v>
       </c>
       <c r="R72" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S72">
         <v>10000</v>
@@ -4918,7 +4927,7 @@
         <v>21</v>
       </c>
       <c r="N73" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O73" t="s">
         <v>27</v>
@@ -4930,7 +4939,7 @@
         <v>74.453514</v>
       </c>
       <c r="R73" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S73">
         <v>10000</v>
@@ -4977,7 +4986,7 @@
         <v>21</v>
       </c>
       <c r="N74" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O74" t="s">
         <v>27</v>
@@ -4989,7 +4998,7 @@
         <v>74.453514</v>
       </c>
       <c r="R74" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S74">
         <v>30720</v>
@@ -5036,7 +5045,7 @@
         <v>21</v>
       </c>
       <c r="N75" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O75" t="s">
         <v>27</v>
@@ -5048,7 +5057,7 @@
         <v>74.453514</v>
       </c>
       <c r="R75" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S75">
         <v>29640</v>
@@ -5095,7 +5104,7 @@
         <v>21</v>
       </c>
       <c r="N76" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O76" t="s">
         <v>27</v>
@@ -5107,7 +5116,7 @@
         <v>74.453514</v>
       </c>
       <c r="R76" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S76">
         <v>28460</v>
@@ -5154,7 +5163,7 @@
         <v>21</v>
       </c>
       <c r="N77" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O77" t="s">
         <v>27</v>
@@ -5166,7 +5175,7 @@
         <v>74.453514</v>
       </c>
       <c r="R77" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S77">
         <v>15353</v>
@@ -5213,7 +5222,7 @@
         <v>21</v>
       </c>
       <c r="N78" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O78" t="s">
         <v>27</v>
@@ -5225,7 +5234,7 @@
         <v>74.453514</v>
       </c>
       <c r="R78" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S78">
         <v>20480</v>
@@ -5272,7 +5281,7 @@
         <v>21</v>
       </c>
       <c r="N79" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O79" t="s">
         <v>27</v>
@@ -5284,7 +5293,7 @@
         <v>74.453514</v>
       </c>
       <c r="R79" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S79">
         <v>20480</v>
@@ -5331,7 +5340,7 @@
         <v>21</v>
       </c>
       <c r="N80" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O80" t="s">
         <v>27</v>
@@ -5343,7 +5352,7 @@
         <v>74.453514</v>
       </c>
       <c r="R80" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S80">
         <v>15360</v>
@@ -5390,7 +5399,7 @@
         <v>21</v>
       </c>
       <c r="N81" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O81" t="s">
         <v>27</v>
@@ -5402,7 +5411,7 @@
         <v>74.18179719</v>
       </c>
       <c r="R81" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S81">
         <v>1314.5</v>
@@ -5449,7 +5458,7 @@
         <v>21</v>
       </c>
       <c r="N82" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="O82" t="s">
         <v>27</v>
@@ -5461,7 +5470,7 @@
         <v>74.18230296</v>
       </c>
       <c r="R82" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S82">
         <v>52394.5</v>
@@ -5508,7 +5517,7 @@
         <v>21</v>
       </c>
       <c r="N83" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="O83" t="s">
         <v>27</v>
@@ -5520,7 +5529,7 @@
         <v>74.46541999999999</v>
       </c>
       <c r="R83" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S83">
         <v>150000</v>
@@ -5567,7 +5576,7 @@
         <v>21</v>
       </c>
       <c r="N84" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="O84" t="s">
         <v>27</v>
@@ -5579,7 +5588,7 @@
         <v>74.46541999999999</v>
       </c>
       <c r="R84" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S84">
         <v>150000</v>
